--- a/assets/constructions/examples/ctd_mib_3075.xlsx
+++ b/assets/constructions/examples/ctd_mib_3075.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,65 +584,79 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>063A06045-05-19-022050</t>
+          <t>FM45-200-60-10T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LINEPRO 06045</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>75</v>
-      </c>
+          <t>FM45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>63</v>
       </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50</v>
-      </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SE...T/W 1204</t>
+          <t>SEHT1204</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx060</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ISO_SE1204H</t>
+          <t>DER_SSSDR:12</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -654,7 +668,9 @@
       <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -671,15 +687,21 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
+          <t>2017-2018/DEREK INTEGRATED CATALOG</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FP75-300-60-16T</t>
+          <t>SE45-80-25.4-5T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -689,47 +711,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FP75</t>
+          <t>SE45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>25.4</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>22.4</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>SPKN1203/SPKN1504</t>
+          <t>SEKT1204</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx060</t>
+          <t>ISO_6462:FDAxx025.4</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ISO_SP1504W</t>
+          <t>ISO_SE1204H</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -752,13 +774,13 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>SP1504_W</t>
+          <t>SE1204_H</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -768,82 +790,88 @@
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>200A90945-14-06-U060063</t>
+          <t>SMSE12-050-A22-040-4T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>BRICE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PLUS 90945</t>
+          <t>Brimill</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>213</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>8.890000000000001</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SN… 1206</t>
+          <t>SEHT/W1204</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx060</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PALB_SN1206H</t>
+          <t>ISO_SE1204H</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -855,15 +883,21 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
+          <t>2022/BRICE</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PE-80-25.4-5T</t>
+          <t>HN45-200-60-12T-R</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -873,47 +907,49 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PE75</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>HN45</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>211.7</v>
+      </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>25.4</v>
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>5.85</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>APMT1604</t>
+          <t>HNGX0907ANSN-R</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx025.4</t>
+          <t>ISO_6462:FDAxx060</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>DER_AP1604H</t>
+          <t>DER_HN0907H</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -936,13 +972,13 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>AP1604_H</t>
+          <t>HN0907_H</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -952,11 +988,25 @@
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>557.72</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>45718.48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M1200HD100Z06HN09</t>
+          <t>M1200D063Z06HN07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,23 +1016,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M1200HD</t>
+          <t>M1200MINI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>108.5</v>
+        <v>71.7</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -992,23 +1042,23 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>6300</v>
+        <v>10100</v>
       </c>
       <c r="M6" t="n">
-        <v>1.61</v>
+        <v>0.65</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>WIDIA_XHN0905H</t>
+          <t>WIDIA_XHN0704H</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1031,18 +1081,18 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>WID_XHN0905_H</t>
+          <t>WID_XHN0704_H</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>WID_M1200H_431</t>
+          <t>WID_M1200D_82</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1051,6 +1101,12 @@
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
